--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486494_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486494_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0351</v>
+        <v>0.8803</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.6819</v>
+        <v>-0.7224</v>
       </c>
       <c r="F2" t="n">
-        <v>2.717</v>
+        <v>1.6027</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8142</v>
+        <v>0.855</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6325</v>
+        <v>1.3746</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1817</v>
+        <v>-0.5195</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0598</v>
+        <v>0.6463</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1164</v>
+        <v>0.9125</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0566</v>
+        <v>-0.2661</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2456</v>
+        <v>0.2087</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4838</v>
+        <v>0.4621</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2382</v>
+        <v>-0.2534</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6559</v>
+        <v>0.0252</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7619</v>
+        <v>-0.2812</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4177</v>
+        <v>0.3064</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.625</v>
+        <v>0.7667</v>
       </c>
       <c r="E3" t="n">
-        <v>2.075</v>
+        <v>2.0317</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.45</v>
+        <v>-1.2651</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5203</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3204</v>
+        <v>0.4621</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5756</v>
+        <v>0.5324</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2552</v>
+        <v>-0.0703</v>
       </c>
       <c r="V3" t="n">
         <v>1.695</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.408</v>
+        <v>0.7589</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1947</v>
+        <v>-1.5882</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6027</v>
+        <v>2.3471</v>
       </c>
       <c r="G4" t="n">
-        <v>0.855</v>
+        <v>0.8142</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3746</v>
+        <v>0.6325</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5195</v>
+        <v>0.1817</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6463</v>
+        <v>1.0598</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9125</v>
+        <v>1.1164</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2661</v>
+        <v>-0.0566</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2087</v>
+        <v>-0.2456</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4621</v>
+        <v>-0.4838</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2534</v>
+        <v>0.2382</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.447</v>
+        <v>0.3797</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.6681</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3064</v>
+        <v>1.0479</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3756</v>
+        <v>0.4373</v>
       </c>
       <c r="E5" t="n">
         <v>0.0365</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3391</v>
+        <v>0.4008</v>
       </c>
       <c r="G5" t="n">
         <v>0.4835</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2105</v>
+        <v>0.2173</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3745</v>
+        <v>-0.306</v>
       </c>
       <c r="F6" t="n">
-        <v>0.585</v>
+        <v>0.5233</v>
       </c>
       <c r="G6" t="n">
         <v>0.1831</v>
@@ -922,13 +922,13 @@
         <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1901</v>
+        <v>-0.1833</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.411</v>
+        <v>-0.3425</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2209</v>
+        <v>0.1592</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3141</v>
+        <v>-0.1214</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1074</v>
+        <v>0.3787</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7934</v>
+        <v>-0.5001</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3144</v>
+        <v>-1.0317</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7812</v>
+        <v>1.1223</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5331</v>
+        <v>-2.1539</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.825</v>
+        <v>0.5541</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8633</v>
+        <v>1.2227</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0382</v>
+        <v>-0.6686</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4893</v>
+        <v>-1.5858</v>
       </c>
       <c r="N7" t="n">
-        <v>0.082</v>
+        <v>-0.1004</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5714</v>
+        <v>-1.4854</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0003</v>
+        <v>-0.1772</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8051</v>
+        <v>-0.1754</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1952</v>
+        <v>-0.0018</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.9731</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0182</v>
+        <v>-1.8897</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.9167</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0317</v>
+        <v>-1.3144</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1223</v>
+        <v>-0.7812</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1539</v>
+        <v>-0.5331</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5541</v>
+        <v>-0.825</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2227</v>
+        <v>-0.8633</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6686</v>
+        <v>0.0382</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5858</v>
+        <v>-0.4893</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1004</v>
+        <v>0.082</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4854</v>
+        <v>-0.5714</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7227</v>
+        <v>0.3413</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.536</v>
+        <v>0.0228</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1867</v>
+        <v>0.3184</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8973</v>
+        <v>-1.1871</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7301</v>
+        <v>-0.7734</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1671</v>
+        <v>-0.4137</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5393</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7741</v>
+        <v>0.4843</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0277</v>
+        <v>-0.0156</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.4999</v>
       </c>
       <c r="V9" t="n">
         <v>0.3904</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5538</v>
+        <v>-1.8532</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6744</v>
+        <v>-1.3453</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1205</v>
+        <v>-0.5079</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1686</v>
+        <v>-1.4716</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0306</v>
+        <v>0.2433</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.138</v>
+        <v>-1.7149</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3094</v>
+        <v>0.6306</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2372</v>
+        <v>0.4777</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5467</v>
+        <v>0.153</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8592</v>
+        <v>-2.1022</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2679</v>
+        <v>-0.2344</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5913</v>
+        <v>-1.8679</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0498</v>
+        <v>0.4672</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1899</v>
+        <v>0.3954</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2397</v>
+        <v>0.0718</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.2838</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0326</v>
+        <v>-1.9168</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3706</v>
+        <v>-3.6059</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.662</v>
+        <v>1.689</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4716</v>
+        <v>-2.1686</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2433</v>
+        <v>-0.0306</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7149</v>
+        <v>-2.138</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6306</v>
+        <v>-1.3094</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4777</v>
+        <v>0.2372</v>
       </c>
       <c r="L11" t="n">
-        <v>0.153</v>
+        <v>-1.5467</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1022</v>
+        <v>-0.8592</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2344</v>
+        <v>-0.2679</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8679</v>
+        <v>-0.5913</v>
       </c>
       <c r="P11" t="n">
-        <v>0.435</v>
+        <v>-0.435</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2878</v>
+        <v>0.6868</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3701</v>
+        <v>-0.1214</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0823</v>
+        <v>0.8081</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2838</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.2838</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1803</v>
+        <v>-2.972</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7261</v>
+        <v>-1.9186</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4541</v>
+        <v>-1.0534</v>
       </c>
       <c r="G12" t="n">
         <v>-4.29</v>
@@ -1390,13 +1390,13 @@
         <v>2.6101</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4128</v>
+        <v>-0.2046</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2654</v>
+        <v>-0.4578</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1475</v>
+        <v>0.2532</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.9907</v>
+        <v>-5.9631</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.73</v>
+        <v>-9.7026</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7395</v>
+        <v>3.7394</v>
       </c>
       <c r="G13" t="n">
         <v>-9.0001</v>
@@ -1447,7 +1447,7 @@
         <v>4.093299999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8685</v>
+        <v>-0.8684999999999996</v>
       </c>
       <c r="M13" t="n">
         <v>-12.2249</v>
@@ -1468,13 +1468,13 @@
         <v>14.1379</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2078</v>
+        <v>2.2352</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1392</v>
+        <v>-1.1114</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3468</v>
+        <v>3.3465</v>
       </c>
       <c r="V13" t="n">
         <v>0.8015999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7102</v>
+        <v>5.1265</v>
       </c>
       <c r="E14" t="n">
         <v>4.662</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0483</v>
+        <v>0.4645</v>
       </c>
       <c r="G14" t="n">
         <v>3.8125</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1251</v>
+        <v>0.2911</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2704</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1453</v>
+        <v>0.5615</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9347</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6903</v>
+        <v>3.5349</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9445</v>
+        <v>1.6093</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7458</v>
+        <v>1.9256</v>
       </c>
       <c r="G15" t="n">
         <v>1.8328</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2501</v>
+        <v>0.0946</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1454</v>
+        <v>-0.4807</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3955</v>
+        <v>0.5753</v>
       </c>
       <c r="V15" t="n">
         <v>2.2599</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0889</v>
+        <v>3.0308</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9586</v>
+        <v>1.4582</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1302</v>
+        <v>1.5726</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3452</v>
+        <v>5.1023</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3228</v>
+        <v>-0.2645</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0223</v>
+        <v>5.3669</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6329</v>
+        <v>5.246</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4417</v>
+        <v>0.1372</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1912</v>
+        <v>5.1087</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2878</v>
+        <v>-0.1436</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1188</v>
+        <v>-0.4018</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1689</v>
+        <v>0.2582</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0875</v>
+        <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8737</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4132</v>
+        <v>-0.5251</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4605</v>
+        <v>0.4536</v>
       </c>
       <c r="V16" t="n">
         <v>-1.13</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5935</v>
+        <v>1.5265</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8994</v>
+        <v>-2.0846</v>
       </c>
       <c r="F17" t="n">
-        <v>0.694</v>
+        <v>3.6111</v>
       </c>
       <c r="G17" t="n">
-        <v>5.1023</v>
+        <v>0.5082</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2645</v>
+        <v>0.313</v>
       </c>
       <c r="I17" t="n">
-        <v>5.3669</v>
+        <v>0.1952</v>
       </c>
       <c r="J17" t="n">
-        <v>5.246</v>
+        <v>0.3849</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1372</v>
+        <v>0.3832</v>
       </c>
       <c r="L17" t="n">
-        <v>5.1087</v>
+        <v>0.0016</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1436</v>
+        <v>0.1233</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4018</v>
+        <v>-0.0703</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2582</v>
+        <v>0.1936</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5088</v>
+        <v>0.1472</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0839</v>
+        <v>-0.2944</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4249</v>
+        <v>0.4416</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.13</v>
+        <v>1.0886</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>1.0886</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9406</v>
+        <v>1.2189</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5317</v>
+        <v>0.6669</v>
       </c>
       <c r="F18" t="n">
-        <v>3.4723</v>
+        <v>0.5521</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5082</v>
+        <v>-0.8817</v>
       </c>
       <c r="H18" t="n">
-        <v>0.313</v>
+        <v>-1.1224</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1952</v>
+        <v>0.2407</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3849</v>
+        <v>-0.1134</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3832</v>
+        <v>-0.6721</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0016</v>
+        <v>0.5587</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1233</v>
+        <v>-0.7683</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0703</v>
+        <v>-0.4504</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1936</v>
+        <v>-0.318</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4386</v>
+        <v>-0.1169</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.3497</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3028</v>
+        <v>0.2328</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0886</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.0886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6063</v>
+        <v>0.7992</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3316</v>
+        <v>0.6175</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2746</v>
+        <v>0.1817</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8817</v>
+        <v>1.3452</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1224</v>
+        <v>1.3228</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2407</v>
+        <v>0.0223</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1134</v>
+        <v>1.6329</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6721</v>
+        <v>1.4417</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5587</v>
+        <v>0.1912</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7683</v>
+        <v>-0.2878</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4504</v>
+        <v>-0.1188</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.318</v>
+        <v>-0.1689</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7295</v>
+        <v>0.584</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.0721</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0446</v>
+        <v>0.5119</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5476</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5777</v>
+        <v>-0.3542</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1254</v>
+        <v>0.9404</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1751</v>
@@ -2014,13 +2014,13 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1473</v>
+        <v>-0.1088</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6746</v>
+        <v>0.4897</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4736</v>
+        <v>-0.0086</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2158</v>
+        <v>-1.9923</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7422</v>
+        <v>1.9837</v>
       </c>
       <c r="G21" t="n">
         <v>-0.328</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3854</v>
+        <v>0.0796</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5179</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3561</v>
+        <v>0.5975</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9613</v>
+        <v>-1.8983</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0493</v>
+        <v>-4.1611</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0881</v>
+        <v>2.2628</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5532</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1798</v>
+        <v>0.2427</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2019</v>
+        <v>-0.3136</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3816</v>
+        <v>0.5564</v>
       </c>
       <c r="V22" t="n">
         <v>0.9347</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7519</v>
+        <v>-4.6902</v>
       </c>
       <c r="E23" t="n">
         <v>-1.9011</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8508</v>
+        <v>-2.7892</v>
       </c>
       <c r="G23" t="n">
         <v>-0.663</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1764</v>
+        <v>-0.1148</v>
       </c>
       <c r="T23" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8249</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.990600000000001</v>
+        <v>9.225899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.479500000000001</v>
+        <v>-1.4794</v>
       </c>
       <c r="F24" t="n">
-        <v>8.470099999999999</v>
+        <v>10.7053</v>
       </c>
       <c r="G24" t="n">
         <v>9</v>
@@ -2302,7 +2302,7 @@
         <v>12.2248</v>
       </c>
       <c r="K24" t="n">
-        <v>1.841399999999999</v>
+        <v>1.8414</v>
       </c>
       <c r="L24" t="n">
         <v>10.3832</v>
@@ -2317,7 +2317,7 @@
         <v>0.8684999999999998</v>
       </c>
       <c r="P24" t="n">
-        <v>9.999999999976694e-05</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="Q24" t="n">
         <v>-14.1379</v>
@@ -2326,13 +2326,13 @@
         <v>14.1379</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2075</v>
+        <v>1.0272</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.3467</v>
+        <v>-3.3466</v>
       </c>
       <c r="U24" t="n">
-        <v>2.139</v>
+        <v>4.374000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8015999999999996</v>
